--- a/data/processed/CRU_TS_4.09/00 abbreviations.xlsx
+++ b/data/processed/CRU_TS_4.09/00 abbreviations.xlsx
@@ -110,8 +110,7 @@
     <t>svp-vap_kpa</t>
   </si>
   <si>
-    <t xml:space="preserve">Since the vap data is not observed but gridded, VPD sometimes turned out to be below 0. The values were calibrated so that all values at the site are above 0 (the absolute value of the negative minimum at the site was added to each value).
-</t>
+    <t>Since the vap data is not observed but gridded, VPD sometimes turned out to be below 0. The values were calibrated so that all values at the site are above 0 (the absolute value of the negative minimum at the site was added to each value).</t>
   </si>
   <si>
     <t xml:space="preserve">rhm </t>
@@ -490,8 +489,8 @@
     <col min="1" max="1" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="2" max="2" style="3" width="50.86214285714286" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="3" width="34.86214285714286" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="3" width="22.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="3" width="48.86214285714286" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="3" width="37.14785714285715" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
